--- a/t1_confection/A1_Outputs/A1_Outputs_NDC+ELC/A-O_Demand.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_NDC+ELC/A-O_Demand.xlsx
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ19"/>
+  <dimension ref="A1:AJ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.85546875" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -750,88 +750,88 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>611.17</v>
+        <v>524.49</v>
       </c>
       <c r="J2" t="n">
-        <v>588.9400000000001</v>
+        <v>506.39</v>
       </c>
       <c r="K2" t="n">
-        <v>588.03</v>
+        <v>512</v>
       </c>
       <c r="L2" t="n">
-        <v>600.02</v>
+        <v>518.55</v>
       </c>
       <c r="M2" t="n">
-        <v>612</v>
+        <v>525.15</v>
       </c>
       <c r="N2" t="n">
-        <v>623.99</v>
+        <v>531.79</v>
       </c>
       <c r="O2" t="n">
-        <v>635.97</v>
+        <v>538.48</v>
       </c>
       <c r="P2" t="n">
-        <v>647.95</v>
+        <v>545.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>662.34</v>
+        <v>551.96</v>
       </c>
       <c r="R2" t="n">
-        <v>676.73</v>
+        <v>558.77</v>
       </c>
       <c r="S2" t="n">
-        <v>691.12</v>
+        <v>565.62</v>
       </c>
       <c r="T2" t="n">
-        <v>705.5</v>
+        <v>572.5</v>
       </c>
       <c r="U2" t="n">
-        <v>719.89</v>
+        <v>579.4299999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>735.12</v>
+        <v>586.4</v>
       </c>
       <c r="W2" t="n">
-        <v>750.35</v>
+        <v>593.42</v>
       </c>
       <c r="X2" t="n">
-        <v>765.58</v>
+        <v>600.47</v>
       </c>
       <c r="Y2" t="n">
-        <v>780.8200000000001</v>
+        <v>607.5700000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>796.05</v>
+        <v>614.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>810.9299999999999</v>
+        <v>621.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>825.8099999999999</v>
+        <v>629.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>840.7</v>
+        <v>636.36</v>
       </c>
       <c r="AD2" t="n">
-        <v>855.58</v>
+        <v>643.66</v>
       </c>
       <c r="AE2" t="n">
-        <v>870.46</v>
+        <v>651</v>
       </c>
       <c r="AF2" t="n">
-        <v>885.64</v>
+        <v>658.38</v>
       </c>
       <c r="AG2" t="n">
-        <v>900.8200000000001</v>
+        <v>665.8099999999999</v>
       </c>
       <c r="AH2" t="n">
-        <v>916</v>
+        <v>673.28</v>
       </c>
       <c r="AI2" t="n">
-        <v>931.1799999999999</v>
+        <v>680.78</v>
       </c>
       <c r="AJ2" t="n">
-        <v>946.35</v>
+        <v>688.33</v>
       </c>
     </row>
     <row r="3">
@@ -874,88 +874,88 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>48.22</v>
+        <v>42.81</v>
       </c>
       <c r="J3" t="n">
-        <v>49.89</v>
+        <v>45.15</v>
       </c>
       <c r="K3" t="n">
-        <v>52.46</v>
+        <v>48.63</v>
       </c>
       <c r="L3" t="n">
-        <v>54.88</v>
+        <v>51.65</v>
       </c>
       <c r="M3" t="n">
-        <v>57.3</v>
+        <v>54.69</v>
       </c>
       <c r="N3" t="n">
-        <v>59.73</v>
+        <v>57.77</v>
       </c>
       <c r="O3" t="n">
-        <v>62.15</v>
+        <v>60.87</v>
       </c>
       <c r="P3" t="n">
-        <v>64.56999999999999</v>
+        <v>64</v>
       </c>
       <c r="Q3" t="n">
-        <v>67.27</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>69.97</v>
+        <v>70.34</v>
       </c>
       <c r="S3" t="n">
-        <v>72.66</v>
+        <v>73.55</v>
       </c>
       <c r="T3" t="n">
-        <v>75.36</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>78.06</v>
+        <v>80.05</v>
       </c>
       <c r="V3" t="n">
-        <v>81.15000000000001</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>84.23999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="X3" t="n">
-        <v>87.33</v>
+        <v>90.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>90.42</v>
+        <v>93.39</v>
       </c>
       <c r="Z3" t="n">
-        <v>93.51000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>97.04000000000001</v>
+        <v>100.23</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.57</v>
+        <v>103.69</v>
       </c>
       <c r="AC3" t="n">
-        <v>104.1</v>
+        <v>107.17</v>
       </c>
       <c r="AD3" t="n">
-        <v>107.63</v>
+        <v>110.69</v>
       </c>
       <c r="AE3" t="n">
-        <v>111.16</v>
+        <v>114.23</v>
       </c>
       <c r="AF3" t="n">
-        <v>115.22</v>
+        <v>117.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>119.27</v>
+        <v>121.39</v>
       </c>
       <c r="AH3" t="n">
-        <v>123.33</v>
+        <v>125.02</v>
       </c>
       <c r="AI3" t="n">
-        <v>127.39</v>
+        <v>128.67</v>
       </c>
       <c r="AJ3" t="n">
-        <v>131.44</v>
+        <v>132.35</v>
       </c>
     </row>
     <row r="4">
@@ -998,88 +998,88 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2268.28</v>
+        <v>2599.63</v>
       </c>
       <c r="J4" t="n">
-        <v>2250.4</v>
+        <v>2637.58</v>
       </c>
       <c r="K4" t="n">
-        <v>2276.48</v>
+        <v>2732.79</v>
       </c>
       <c r="L4" t="n">
-        <v>2276.48</v>
+        <v>2802.48</v>
       </c>
       <c r="M4" t="n">
-        <v>2276.48</v>
+        <v>2872.73</v>
       </c>
       <c r="N4" t="n">
-        <v>2276.48</v>
+        <v>2943.54</v>
       </c>
       <c r="O4" t="n">
-        <v>2276.48</v>
+        <v>3014.9</v>
       </c>
       <c r="P4" t="n">
-        <v>2276.48</v>
+        <v>3086.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>2297.99</v>
+        <v>3159.31</v>
       </c>
       <c r="R4" t="n">
-        <v>2319.51</v>
+        <v>3232.35</v>
       </c>
       <c r="S4" t="n">
-        <v>2341.05</v>
+        <v>3305.95</v>
       </c>
       <c r="T4" t="n">
-        <v>2362.56</v>
+        <v>3380.11</v>
       </c>
       <c r="U4" t="n">
-        <v>2384.08</v>
+        <v>3454.82</v>
       </c>
       <c r="V4" t="n">
-        <v>2424.3</v>
+        <v>3530.09</v>
       </c>
       <c r="W4" t="n">
-        <v>2464.55</v>
+        <v>3605.93</v>
       </c>
       <c r="X4" t="n">
-        <v>2504.79</v>
+        <v>3682.32</v>
       </c>
       <c r="Y4" t="n">
-        <v>2545.03</v>
+        <v>3759.26</v>
       </c>
       <c r="Z4" t="n">
-        <v>2585.28</v>
+        <v>3836.77</v>
       </c>
       <c r="AA4" t="n">
-        <v>2624.3</v>
+        <v>3914.84</v>
       </c>
       <c r="AB4" t="n">
-        <v>2663.31</v>
+        <v>3993.46</v>
       </c>
       <c r="AC4" t="n">
-        <v>2702.33</v>
+        <v>4072.64</v>
       </c>
       <c r="AD4" t="n">
-        <v>2741.33</v>
+        <v>4152.38</v>
       </c>
       <c r="AE4" t="n">
-        <v>2780.36</v>
+        <v>4232.68</v>
       </c>
       <c r="AF4" t="n">
-        <v>2819.64</v>
+        <v>4313.54</v>
       </c>
       <c r="AG4" t="n">
-        <v>2858.91</v>
+        <v>4394.95</v>
       </c>
       <c r="AH4" t="n">
-        <v>2898.19</v>
+        <v>4476.92</v>
       </c>
       <c r="AI4" t="n">
-        <v>2937.47</v>
+        <v>4559.46</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2976.75</v>
+        <v>4642.54</v>
       </c>
     </row>
     <row r="5">
@@ -1122,88 +1122,88 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>14.87</v>
+        <v>3.87</v>
       </c>
       <c r="J5" t="n">
-        <v>14.87</v>
+        <v>4.12</v>
       </c>
       <c r="K5" t="n">
-        <v>14.87</v>
+        <v>4.39</v>
       </c>
       <c r="L5" t="n">
-        <v>14.87</v>
+        <v>4.66</v>
       </c>
       <c r="M5" t="n">
-        <v>14.87</v>
+        <v>4.94</v>
       </c>
       <c r="N5" t="n">
-        <v>14.87</v>
+        <v>5.21</v>
       </c>
       <c r="O5" t="n">
-        <v>14.87</v>
+        <v>5.49</v>
       </c>
       <c r="P5" t="n">
-        <v>14.87</v>
+        <v>5.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.87</v>
+        <v>6.06</v>
       </c>
       <c r="R5" t="n">
-        <v>14.87</v>
+        <v>6.34</v>
       </c>
       <c r="S5" t="n">
-        <v>14.87</v>
+        <v>6.63</v>
       </c>
       <c r="T5" t="n">
-        <v>14.87</v>
+        <v>6.92</v>
       </c>
       <c r="U5" t="n">
-        <v>14.87</v>
+        <v>7.22</v>
       </c>
       <c r="V5" t="n">
-        <v>14.87</v>
+        <v>7.51</v>
       </c>
       <c r="W5" t="n">
-        <v>14.87</v>
+        <v>7.81</v>
       </c>
       <c r="X5" t="n">
-        <v>14.87</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.87</v>
+        <v>8.42</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.87</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AA5" t="n">
-        <v>14.88</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>14.88</v>
+        <v>9.34</v>
       </c>
       <c r="AC5" t="n">
-        <v>14.89</v>
+        <v>9.65</v>
       </c>
       <c r="AD5" t="n">
-        <v>14.9</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="AE5" t="n">
-        <v>14.9</v>
+        <v>10.29</v>
       </c>
       <c r="AF5" t="n">
-        <v>15.73</v>
+        <v>10.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>16.55</v>
+        <v>10.93</v>
       </c>
       <c r="AH5" t="n">
-        <v>17.37</v>
+        <v>11.26</v>
       </c>
       <c r="AI5" t="n">
-        <v>18.19</v>
+        <v>11.59</v>
       </c>
       <c r="AJ5" t="n">
-        <v>19.02</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="6">
@@ -1246,88 +1246,88 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>271.26</v>
+        <v>302.25</v>
       </c>
       <c r="J6" t="n">
-        <v>271.4</v>
+        <v>318.54</v>
       </c>
       <c r="K6" t="n">
-        <v>271.37</v>
+        <v>336.33</v>
       </c>
       <c r="L6" t="n">
-        <v>271.37</v>
+        <v>354.31</v>
       </c>
       <c r="M6" t="n">
-        <v>271.37</v>
+        <v>372.46</v>
       </c>
       <c r="N6" t="n">
-        <v>271.37</v>
+        <v>390.76</v>
       </c>
       <c r="O6" t="n">
-        <v>271.37</v>
+        <v>409.23</v>
       </c>
       <c r="P6" t="n">
-        <v>271.37</v>
+        <v>427.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>272.87</v>
+        <v>446.65</v>
       </c>
       <c r="R6" t="n">
-        <v>274.37</v>
+        <v>465.6</v>
       </c>
       <c r="S6" t="n">
-        <v>275.86</v>
+        <v>484.71</v>
       </c>
       <c r="T6" t="n">
-        <v>277.36</v>
+        <v>503.99</v>
       </c>
       <c r="U6" t="n">
-        <v>278.85</v>
+        <v>523.4299999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>284.91</v>
+        <v>543.02</v>
       </c>
       <c r="W6" t="n">
-        <v>290.97</v>
+        <v>562.78</v>
       </c>
       <c r="X6" t="n">
-        <v>297.03</v>
+        <v>582.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>303.09</v>
+        <v>602.78</v>
       </c>
       <c r="Z6" t="n">
-        <v>309.16</v>
+        <v>623.03</v>
       </c>
       <c r="AA6" t="n">
-        <v>315.46</v>
+        <v>643.4299999999999</v>
       </c>
       <c r="AB6" t="n">
-        <v>321.76</v>
+        <v>664</v>
       </c>
       <c r="AC6" t="n">
-        <v>328.07</v>
+        <v>684.73</v>
       </c>
       <c r="AD6" t="n">
-        <v>334.37</v>
+        <v>705.62</v>
       </c>
       <c r="AE6" t="n">
-        <v>340.68</v>
+        <v>726.67</v>
       </c>
       <c r="AF6" t="n">
-        <v>346.97</v>
+        <v>747.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>353.26</v>
+        <v>769.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>359.55</v>
+        <v>790.79</v>
       </c>
       <c r="AI6" t="n">
-        <v>365.84</v>
+        <v>812.48</v>
       </c>
       <c r="AJ6" t="n">
-        <v>372.13</v>
+        <v>834.34</v>
       </c>
     </row>
     <row r="7">
@@ -1370,88 +1370,88 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>381.42</v>
+        <v>288.23</v>
       </c>
       <c r="J7" t="n">
-        <v>388.96</v>
+        <v>296.14</v>
       </c>
       <c r="K7" t="n">
-        <v>403.26</v>
+        <v>312.39</v>
       </c>
       <c r="L7" t="n">
-        <v>415.05</v>
+        <v>324.75</v>
       </c>
       <c r="M7" t="n">
-        <v>426.83</v>
+        <v>337.23</v>
       </c>
       <c r="N7" t="n">
-        <v>438.62</v>
+        <v>349.81</v>
       </c>
       <c r="O7" t="n">
-        <v>450.41</v>
+        <v>362.5</v>
       </c>
       <c r="P7" t="n">
-        <v>462.19</v>
+        <v>375.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>475.02</v>
+        <v>388.2</v>
       </c>
       <c r="R7" t="n">
-        <v>487.85</v>
+        <v>401.22</v>
       </c>
       <c r="S7" t="n">
-        <v>500.68</v>
+        <v>414.33</v>
       </c>
       <c r="T7" t="n">
-        <v>513.5</v>
+        <v>427.56</v>
       </c>
       <c r="U7" t="n">
-        <v>526.33</v>
+        <v>440.89</v>
       </c>
       <c r="V7" t="n">
-        <v>540.62</v>
+        <v>454.33</v>
       </c>
       <c r="W7" t="n">
-        <v>554.91</v>
+        <v>467.88</v>
       </c>
       <c r="X7" t="n">
-        <v>569.1900000000001</v>
+        <v>481.53</v>
       </c>
       <c r="Y7" t="n">
-        <v>583.48</v>
+        <v>495.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>597.77</v>
+        <v>509.16</v>
       </c>
       <c r="AA7" t="n">
-        <v>613.33</v>
+        <v>523.13</v>
       </c>
       <c r="AB7" t="n">
-        <v>628.89</v>
+        <v>537.21</v>
       </c>
       <c r="AC7" t="n">
-        <v>644.46</v>
+        <v>551.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>660.02</v>
+        <v>565.7</v>
       </c>
       <c r="AE7" t="n">
-        <v>675.59</v>
+        <v>580.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>692.27</v>
+        <v>594.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>708.96</v>
+        <v>609.23</v>
       </c>
       <c r="AH7" t="n">
-        <v>725.64</v>
+        <v>623.95</v>
       </c>
       <c r="AI7" t="n">
-        <v>742.33</v>
+        <v>638.78</v>
       </c>
       <c r="AJ7" t="n">
-        <v>759.01</v>
+        <v>653.72</v>
       </c>
     </row>
     <row r="8">
@@ -1494,88 +1494,88 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>46.71</v>
+        <v>44.28</v>
       </c>
       <c r="J8" t="n">
-        <v>48.51</v>
+        <v>44.68</v>
       </c>
       <c r="K8" t="n">
-        <v>48.82</v>
+        <v>43.8</v>
       </c>
       <c r="L8" t="n">
-        <v>51.52</v>
+        <v>44.92</v>
       </c>
       <c r="M8" t="n">
-        <v>54.23</v>
+        <v>46.04</v>
       </c>
       <c r="N8" t="n">
-        <v>56.93</v>
+        <v>47.18</v>
       </c>
       <c r="O8" t="n">
-        <v>59.64</v>
+        <v>48.32</v>
       </c>
       <c r="P8" t="n">
-        <v>62.35</v>
+        <v>49.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>65.31</v>
+        <v>50.64</v>
       </c>
       <c r="R8" t="n">
-        <v>68.27</v>
+        <v>51.81</v>
       </c>
       <c r="S8" t="n">
-        <v>71.23</v>
+        <v>52.99</v>
       </c>
       <c r="T8" t="n">
-        <v>74.19</v>
+        <v>54.18</v>
       </c>
       <c r="U8" t="n">
-        <v>77.15000000000001</v>
+        <v>55.38</v>
       </c>
       <c r="V8" t="n">
-        <v>80.5</v>
+        <v>56.58</v>
       </c>
       <c r="W8" t="n">
-        <v>83.84999999999999</v>
+        <v>57.8</v>
       </c>
       <c r="X8" t="n">
-        <v>87.19</v>
+        <v>59.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>90.54000000000001</v>
+        <v>60.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>93.89</v>
+        <v>61.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>97.53</v>
+        <v>62.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>101.18</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>104.82</v>
+        <v>65.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>108.46</v>
+        <v>66.56</v>
       </c>
       <c r="AE8" t="n">
-        <v>112.11</v>
+        <v>67.84</v>
       </c>
       <c r="AF8" t="n">
-        <v>115.95</v>
+        <v>69.14</v>
       </c>
       <c r="AG8" t="n">
-        <v>119.78</v>
+        <v>70.44</v>
       </c>
       <c r="AH8" t="n">
-        <v>123.62</v>
+        <v>71.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>127.46</v>
+        <v>73.08</v>
       </c>
       <c r="AJ8" t="n">
-        <v>131.29</v>
+        <v>74.41</v>
       </c>
     </row>
     <row r="9">
@@ -1618,88 +1618,88 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>66.8</v>
+        <v>86.09</v>
       </c>
       <c r="J9" t="n">
-        <v>66.92</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>67.03</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>71.7</v>
+        <v>96.08</v>
       </c>
       <c r="M9" t="n">
-        <v>76.37</v>
+        <v>99.61</v>
       </c>
       <c r="N9" t="n">
-        <v>81.04000000000001</v>
+        <v>103.17</v>
       </c>
       <c r="O9" t="n">
-        <v>85.7</v>
+        <v>106.77</v>
       </c>
       <c r="P9" t="n">
-        <v>90.37</v>
+        <v>110.39</v>
       </c>
       <c r="Q9" t="n">
-        <v>95.44</v>
+        <v>114.05</v>
       </c>
       <c r="R9" t="n">
-        <v>100.51</v>
+        <v>117.73</v>
       </c>
       <c r="S9" t="n">
-        <v>105.58</v>
+        <v>121.44</v>
       </c>
       <c r="T9" t="n">
-        <v>110.65</v>
+        <v>125.19</v>
       </c>
       <c r="U9" t="n">
-        <v>115.72</v>
+        <v>128.96</v>
       </c>
       <c r="V9" t="n">
-        <v>121.48</v>
+        <v>132.77</v>
       </c>
       <c r="W9" t="n">
-        <v>127.23</v>
+        <v>136.6</v>
       </c>
       <c r="X9" t="n">
-        <v>132.98</v>
+        <v>140.47</v>
       </c>
       <c r="Y9" t="n">
-        <v>138.73</v>
+        <v>144.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>144.49</v>
+        <v>148.29</v>
       </c>
       <c r="AA9" t="n">
-        <v>150.83</v>
+        <v>152.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>157.18</v>
+        <v>156.23</v>
       </c>
       <c r="AC9" t="n">
-        <v>163.53</v>
+        <v>160.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>169.88</v>
+        <v>164.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>176.23</v>
+        <v>168.37</v>
       </c>
       <c r="AF9" t="n">
-        <v>183.07</v>
+        <v>172.48</v>
       </c>
       <c r="AG9" t="n">
-        <v>189.91</v>
+        <v>176.61</v>
       </c>
       <c r="AH9" t="n">
-        <v>196.75</v>
+        <v>180.78</v>
       </c>
       <c r="AI9" t="n">
-        <v>203.59</v>
+        <v>184.98</v>
       </c>
       <c r="AJ9" t="n">
-        <v>210.44</v>
+        <v>189.2</v>
       </c>
     </row>
     <row r="10">
@@ -1742,88 +1742,88 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>99.68000000000001</v>
+        <v>129.57</v>
       </c>
       <c r="J10" t="n">
-        <v>102.97</v>
+        <v>137.75</v>
       </c>
       <c r="K10" t="n">
-        <v>99.95</v>
+        <v>140.3</v>
       </c>
       <c r="L10" t="n">
-        <v>103.13</v>
+        <v>146.86</v>
       </c>
       <c r="M10" t="n">
-        <v>106.32</v>
+        <v>153.47</v>
       </c>
       <c r="N10" t="n">
-        <v>109.5</v>
+        <v>160.15</v>
       </c>
       <c r="O10" t="n">
-        <v>112.68</v>
+        <v>166.88</v>
       </c>
       <c r="P10" t="n">
-        <v>115.87</v>
+        <v>173.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>119.33</v>
+        <v>180.51</v>
       </c>
       <c r="R10" t="n">
-        <v>122.8</v>
+        <v>187.42</v>
       </c>
       <c r="S10" t="n">
-        <v>126.27</v>
+        <v>194.38</v>
       </c>
       <c r="T10" t="n">
-        <v>129.73</v>
+        <v>201.41</v>
       </c>
       <c r="U10" t="n">
-        <v>133.2</v>
+        <v>208.49</v>
       </c>
       <c r="V10" t="n">
-        <v>137.2</v>
+        <v>215.62</v>
       </c>
       <c r="W10" t="n">
-        <v>141.2</v>
+        <v>222.82</v>
       </c>
       <c r="X10" t="n">
-        <v>145.2</v>
+        <v>230.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>149.21</v>
+        <v>237.39</v>
       </c>
       <c r="Z10" t="n">
-        <v>153.21</v>
+        <v>244.76</v>
       </c>
       <c r="AA10" t="n">
-        <v>157.85</v>
+        <v>252.19</v>
       </c>
       <c r="AB10" t="n">
-        <v>162.5</v>
+        <v>259.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>167.15</v>
+        <v>267.22</v>
       </c>
       <c r="AD10" t="n">
-        <v>171.79</v>
+        <v>274.82</v>
       </c>
       <c r="AE10" t="n">
-        <v>176.44</v>
+        <v>282.48</v>
       </c>
       <c r="AF10" t="n">
-        <v>181.73</v>
+        <v>290.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>187.02</v>
+        <v>297.98</v>
       </c>
       <c r="AH10" t="n">
-        <v>192.3</v>
+        <v>305.81</v>
       </c>
       <c r="AI10" t="n">
-        <v>197.59</v>
+        <v>313.7</v>
       </c>
       <c r="AJ10" t="n">
-        <v>202.88</v>
+        <v>321.65</v>
       </c>
     </row>
     <row r="11">
@@ -1866,88 +1866,88 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>41.19</v>
+        <v>47.17</v>
       </c>
       <c r="J11" t="n">
-        <v>41.03</v>
+        <v>48.54</v>
       </c>
       <c r="K11" t="n">
-        <v>39.49</v>
+        <v>48.77</v>
       </c>
       <c r="L11" t="n">
-        <v>39.49</v>
+        <v>50.55</v>
       </c>
       <c r="M11" t="n">
-        <v>39.49</v>
+        <v>52.35</v>
       </c>
       <c r="N11" t="n">
-        <v>39.49</v>
+        <v>54.16</v>
       </c>
       <c r="O11" t="n">
-        <v>39.49</v>
+        <v>55.99</v>
       </c>
       <c r="P11" t="n">
-        <v>39.49</v>
+        <v>57.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>39.49</v>
+        <v>59.69</v>
       </c>
       <c r="R11" t="n">
-        <v>39.49</v>
+        <v>61.57</v>
       </c>
       <c r="S11" t="n">
-        <v>39.49</v>
+        <v>63.45</v>
       </c>
       <c r="T11" t="n">
-        <v>39.49</v>
+        <v>65.36</v>
       </c>
       <c r="U11" t="n">
-        <v>39.49</v>
+        <v>67.28</v>
       </c>
       <c r="V11" t="n">
-        <v>42.01</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>44.53</v>
+        <v>71.16</v>
       </c>
       <c r="X11" t="n">
-        <v>47.05</v>
+        <v>73.13</v>
       </c>
       <c r="Y11" t="n">
-        <v>49.56</v>
+        <v>75.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>52.08</v>
+        <v>77.11</v>
       </c>
       <c r="AA11" t="n">
-        <v>60.47</v>
+        <v>79.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>68.84999999999999</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>77.23999999999999</v>
+        <v>83.19</v>
       </c>
       <c r="AD11" t="n">
-        <v>85.62</v>
+        <v>85.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>94.01000000000001</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="AF11" t="n">
-        <v>104.66</v>
+        <v>89.41</v>
       </c>
       <c r="AG11" t="n">
-        <v>115.32</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="AH11" t="n">
-        <v>125.98</v>
+        <v>93.63</v>
       </c>
       <c r="AI11" t="n">
-        <v>136.63</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>147.29</v>
+        <v>97.91</v>
       </c>
     </row>
     <row r="12">
@@ -1990,88 +1990,88 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>33.3</v>
+        <v>43.14</v>
       </c>
       <c r="J12" t="n">
-        <v>33.32</v>
+        <v>44.46</v>
       </c>
       <c r="K12" t="n">
-        <v>33.49</v>
+        <v>46.16</v>
       </c>
       <c r="L12" t="n">
-        <v>33.49</v>
+        <v>47.71</v>
       </c>
       <c r="M12" t="n">
-        <v>33.49</v>
+        <v>49.26</v>
       </c>
       <c r="N12" t="n">
-        <v>33.49</v>
+        <v>50.83</v>
       </c>
       <c r="O12" t="n">
-        <v>33.49</v>
+        <v>52.42</v>
       </c>
       <c r="P12" t="n">
-        <v>33.49</v>
+        <v>54.01</v>
       </c>
       <c r="Q12" t="n">
-        <v>33.49</v>
+        <v>55.62</v>
       </c>
       <c r="R12" t="n">
-        <v>33.49</v>
+        <v>57.25</v>
       </c>
       <c r="S12" t="n">
-        <v>33.49</v>
+        <v>58.88</v>
       </c>
       <c r="T12" t="n">
-        <v>33.49</v>
+        <v>60.53</v>
       </c>
       <c r="U12" t="n">
-        <v>33.49</v>
+        <v>62.19</v>
       </c>
       <c r="V12" t="n">
-        <v>33.49</v>
+        <v>63.87</v>
       </c>
       <c r="W12" t="n">
-        <v>33.49</v>
+        <v>65.55</v>
       </c>
       <c r="X12" t="n">
-        <v>33.49</v>
+        <v>67.25</v>
       </c>
       <c r="Y12" t="n">
-        <v>33.49</v>
+        <v>68.97</v>
       </c>
       <c r="Z12" t="n">
-        <v>33.49</v>
+        <v>70.69</v>
       </c>
       <c r="AA12" t="n">
-        <v>33.49</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="AB12" t="n">
-        <v>33.49</v>
+        <v>74.19</v>
       </c>
       <c r="AC12" t="n">
-        <v>33.49</v>
+        <v>75.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>33.49</v>
+        <v>77.73</v>
       </c>
       <c r="AE12" t="n">
-        <v>33.49</v>
+        <v>79.52</v>
       </c>
       <c r="AF12" t="n">
-        <v>38.18</v>
+        <v>81.33</v>
       </c>
       <c r="AG12" t="n">
-        <v>42.88</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="AH12" t="n">
-        <v>47.58</v>
+        <v>84.98</v>
       </c>
       <c r="AI12" t="n">
-        <v>52.28</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>56.97</v>
+        <v>88.68000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -2114,88 +2114,88 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1206.65</v>
+        <v>1241.42</v>
       </c>
       <c r="J13" t="n">
-        <v>1238.93</v>
+        <v>1279.49</v>
       </c>
       <c r="K13" t="n">
-        <v>1271.38</v>
+        <v>1324.32</v>
       </c>
       <c r="L13" t="n">
-        <v>1335.71</v>
+        <v>1368.73</v>
       </c>
       <c r="M13" t="n">
-        <v>1400.04</v>
+        <v>1413.51</v>
       </c>
       <c r="N13" t="n">
-        <v>1464.38</v>
+        <v>1458.67</v>
       </c>
       <c r="O13" t="n">
-        <v>1528.71</v>
+        <v>1504.2</v>
       </c>
       <c r="P13" t="n">
-        <v>1593.04</v>
+        <v>1550.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1663.64</v>
+        <v>1596.38</v>
       </c>
       <c r="R13" t="n">
-        <v>1734.23</v>
+        <v>1643.03</v>
       </c>
       <c r="S13" t="n">
-        <v>1804.83</v>
+        <v>1690.06</v>
       </c>
       <c r="T13" t="n">
-        <v>1875.42</v>
+        <v>1737.46</v>
       </c>
       <c r="U13" t="n">
-        <v>1946.02</v>
+        <v>1785.24</v>
       </c>
       <c r="V13" t="n">
-        <v>2022.61</v>
+        <v>1833.39</v>
       </c>
       <c r="W13" t="n">
-        <v>2099.2</v>
+        <v>1881.91</v>
       </c>
       <c r="X13" t="n">
-        <v>2175.79</v>
+        <v>1930.81</v>
       </c>
       <c r="Y13" t="n">
-        <v>2252.39</v>
+        <v>1980.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>2328.98</v>
+        <v>2029.73</v>
       </c>
       <c r="AA13" t="n">
-        <v>2413.98</v>
+        <v>2079.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>2498.99</v>
+        <v>2130.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>2584</v>
+        <v>2180.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>2669.01</v>
+        <v>2232.06</v>
       </c>
       <c r="AE13" t="n">
-        <v>2754.02</v>
+        <v>2283.58</v>
       </c>
       <c r="AF13" t="n">
-        <v>2848.68</v>
+        <v>2335.47</v>
       </c>
       <c r="AG13" t="n">
-        <v>2943.34</v>
+        <v>2387.74</v>
       </c>
       <c r="AH13" t="n">
-        <v>3038</v>
+        <v>2440.38</v>
       </c>
       <c r="AI13" t="n">
-        <v>3132.66</v>
+        <v>2493.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3227.32</v>
+        <v>2546.79</v>
       </c>
     </row>
     <row r="14">
@@ -2238,88 +2238,88 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>19.46</v>
+        <v>20.33</v>
       </c>
       <c r="J14" t="n">
-        <v>19.63</v>
+        <v>21.29</v>
       </c>
       <c r="K14" t="n">
-        <v>19.99</v>
+        <v>22.54</v>
       </c>
       <c r="L14" t="n">
-        <v>19.99</v>
+        <v>23.44</v>
       </c>
       <c r="M14" t="n">
-        <v>19.99</v>
+        <v>24.34</v>
       </c>
       <c r="N14" t="n">
-        <v>19.99</v>
+        <v>25.26</v>
       </c>
       <c r="O14" t="n">
-        <v>19.99</v>
+        <v>26.18</v>
       </c>
       <c r="P14" t="n">
-        <v>19.99</v>
+        <v>27.11</v>
       </c>
       <c r="Q14" t="n">
-        <v>19.99</v>
+        <v>28.04</v>
       </c>
       <c r="R14" t="n">
-        <v>19.99</v>
+        <v>28.99</v>
       </c>
       <c r="S14" t="n">
-        <v>19.99</v>
+        <v>29.94</v>
       </c>
       <c r="T14" t="n">
-        <v>19.99</v>
+        <v>30.9</v>
       </c>
       <c r="U14" t="n">
-        <v>19.99</v>
+        <v>31.87</v>
       </c>
       <c r="V14" t="n">
-        <v>19.99</v>
+        <v>32.85</v>
       </c>
       <c r="W14" t="n">
-        <v>19.99</v>
+        <v>33.83</v>
       </c>
       <c r="X14" t="n">
-        <v>19.99</v>
+        <v>34.83</v>
       </c>
       <c r="Y14" t="n">
-        <v>19.99</v>
+        <v>35.83</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.99</v>
+        <v>36.84</v>
       </c>
       <c r="AA14" t="n">
-        <v>20.13</v>
+        <v>37.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>20.27</v>
+        <v>38.88</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.41</v>
+        <v>39.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>20.55</v>
+        <v>40.95</v>
       </c>
       <c r="AE14" t="n">
-        <v>20.69</v>
+        <v>42</v>
       </c>
       <c r="AF14" t="n">
-        <v>23.99</v>
+        <v>43.05</v>
       </c>
       <c r="AG14" t="n">
-        <v>27.29</v>
+        <v>44.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>30.59</v>
+        <v>45.19</v>
       </c>
       <c r="AI14" t="n">
-        <v>33.88</v>
+        <v>46.27</v>
       </c>
       <c r="AJ14" t="n">
-        <v>37.18</v>
+        <v>47.36</v>
       </c>
     </row>
     <row r="15">
@@ -2362,88 +2362,88 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>70.38</v>
+        <v>51.79</v>
       </c>
       <c r="J15" t="n">
-        <v>73.31999999999999</v>
+        <v>52.92</v>
       </c>
       <c r="K15" t="n">
-        <v>78.38</v>
+        <v>56.46</v>
       </c>
       <c r="L15" t="n">
-        <v>82.89</v>
+        <v>59.32</v>
       </c>
       <c r="M15" t="n">
-        <v>87.39</v>
+        <v>62.2</v>
       </c>
       <c r="N15" t="n">
-        <v>91.90000000000001</v>
+        <v>65.11</v>
       </c>
       <c r="O15" t="n">
-        <v>96.40000000000001</v>
+        <v>68.05</v>
       </c>
       <c r="P15" t="n">
-        <v>100.91</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>105.61</v>
+        <v>74</v>
       </c>
       <c r="R15" t="n">
-        <v>110.31</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>115.02</v>
+        <v>80.05</v>
       </c>
       <c r="T15" t="n">
-        <v>119.72</v>
+        <v>83.11</v>
       </c>
       <c r="U15" t="n">
-        <v>124.42</v>
+        <v>86.2</v>
       </c>
       <c r="V15" t="n">
-        <v>129.36</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>134.31</v>
+        <v>92.45999999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>139.25</v>
+        <v>95.62</v>
       </c>
       <c r="Y15" t="n">
-        <v>144.19</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="Z15" t="n">
-        <v>149.13</v>
+        <v>102.03</v>
       </c>
       <c r="AA15" t="n">
-        <v>154.46</v>
+        <v>105.28</v>
       </c>
       <c r="AB15" t="n">
-        <v>159.8</v>
+        <v>108.54</v>
       </c>
       <c r="AC15" t="n">
-        <v>165.13</v>
+        <v>111.84</v>
       </c>
       <c r="AD15" t="n">
-        <v>170.46</v>
+        <v>115.15</v>
       </c>
       <c r="AE15" t="n">
-        <v>175.79</v>
+        <v>118.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>181.31</v>
+        <v>121.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>186.83</v>
+        <v>125.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>192.34</v>
+        <v>128.68</v>
       </c>
       <c r="AI15" t="n">
-        <v>197.86</v>
+        <v>132.13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>203.38</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="16">
@@ -2486,88 +2486,88 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>257.1</v>
+        <v>223.04</v>
       </c>
       <c r="J16" t="n">
-        <v>266.64</v>
+        <v>233.01</v>
       </c>
       <c r="K16" t="n">
-        <v>275.76</v>
+        <v>243.77</v>
       </c>
       <c r="L16" t="n">
-        <v>284.78</v>
+        <v>254.64</v>
       </c>
       <c r="M16" t="n">
-        <v>293.8</v>
+        <v>265.61</v>
       </c>
       <c r="N16" t="n">
-        <v>302.82</v>
+        <v>276.67</v>
       </c>
       <c r="O16" t="n">
-        <v>311.84</v>
+        <v>287.83</v>
       </c>
       <c r="P16" t="n">
-        <v>320.86</v>
+        <v>299.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>329.98</v>
+        <v>310.44</v>
       </c>
       <c r="R16" t="n">
-        <v>339.1</v>
+        <v>321.88</v>
       </c>
       <c r="S16" t="n">
-        <v>348.22</v>
+        <v>333.42</v>
       </c>
       <c r="T16" t="n">
-        <v>357.34</v>
+        <v>345.06</v>
       </c>
       <c r="U16" t="n">
-        <v>366.46</v>
+        <v>356.79</v>
       </c>
       <c r="V16" t="n">
-        <v>376.03</v>
+        <v>368.62</v>
       </c>
       <c r="W16" t="n">
-        <v>385.61</v>
+        <v>380.55</v>
       </c>
       <c r="X16" t="n">
-        <v>395.19</v>
+        <v>392.57</v>
       </c>
       <c r="Y16" t="n">
-        <v>404.76</v>
+        <v>404.68</v>
       </c>
       <c r="Z16" t="n">
-        <v>414.34</v>
+        <v>416.89</v>
       </c>
       <c r="AA16" t="n">
-        <v>424.34</v>
+        <v>429.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>434.34</v>
+        <v>441.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>444.35</v>
+        <v>454.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>454.35</v>
+        <v>466.69</v>
       </c>
       <c r="AE16" t="n">
-        <v>464.35</v>
+        <v>479.38</v>
       </c>
       <c r="AF16" t="n">
-        <v>474.63</v>
+        <v>492.17</v>
       </c>
       <c r="AG16" t="n">
-        <v>484.91</v>
+        <v>505.05</v>
       </c>
       <c r="AH16" t="n">
-        <v>495.18</v>
+        <v>518.02</v>
       </c>
       <c r="AI16" t="n">
-        <v>505.46</v>
+        <v>531.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>515.74</v>
+        <v>544.26</v>
       </c>
     </row>
     <row r="17">
@@ -2610,88 +2610,88 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-56.77</v>
+        <v>81.55</v>
       </c>
       <c r="J17" t="n">
-        <v>-4.97</v>
+        <v>145.53</v>
       </c>
       <c r="K17" t="n">
-        <v>-33.82</v>
+        <v>129.94</v>
       </c>
       <c r="L17" t="n">
-        <v>-33.82</v>
+        <v>143.32</v>
       </c>
       <c r="M17" t="n">
-        <v>-33.82</v>
+        <v>156.83</v>
       </c>
       <c r="N17" t="n">
-        <v>-33.82</v>
+        <v>170.45</v>
       </c>
       <c r="O17" t="n">
-        <v>-33.82</v>
+        <v>184.2</v>
       </c>
       <c r="P17" t="n">
-        <v>-33.82</v>
+        <v>198.07</v>
       </c>
       <c r="Q17" t="n">
-        <v>-33.82</v>
+        <v>212.06</v>
       </c>
       <c r="R17" t="n">
-        <v>-33.82</v>
+        <v>226.17</v>
       </c>
       <c r="S17" t="n">
-        <v>-33.82</v>
+        <v>240.4</v>
       </c>
       <c r="T17" t="n">
-        <v>-33.82</v>
+        <v>254.76</v>
       </c>
       <c r="U17" t="n">
-        <v>-33.82</v>
+        <v>269.23</v>
       </c>
       <c r="V17" t="n">
-        <v>-31.92</v>
+        <v>283.83</v>
       </c>
       <c r="W17" t="n">
-        <v>-30.01</v>
+        <v>298.55</v>
       </c>
       <c r="X17" t="n">
-        <v>-28.11</v>
+        <v>313.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>-26.21</v>
+        <v>328.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>-24.31</v>
+        <v>343.45</v>
       </c>
       <c r="AA17" t="n">
-        <v>-21.75</v>
+        <v>358.66</v>
       </c>
       <c r="AB17" t="n">
-        <v>-19.19</v>
+        <v>373.99</v>
       </c>
       <c r="AC17" t="n">
-        <v>-16.63</v>
+        <v>389.44</v>
       </c>
       <c r="AD17" t="n">
-        <v>-14.07</v>
+        <v>405.01</v>
       </c>
       <c r="AE17" t="n">
-        <v>-11.51</v>
+        <v>420.71</v>
       </c>
       <c r="AF17" t="n">
-        <v>-8.59</v>
+        <v>436.53</v>
       </c>
       <c r="AG17" t="n">
-        <v>-5.67</v>
+        <v>452.47</v>
       </c>
       <c r="AH17" t="n">
-        <v>-2.75</v>
+        <v>468.53</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.17</v>
+        <v>484.71</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.09</v>
+        <v>501.02</v>
       </c>
     </row>
     <row r="18">
@@ -2734,88 +2734,88 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>23.39</v>
+        <v>27.94</v>
       </c>
       <c r="J18" t="n">
-        <v>24.64</v>
+        <v>29.86</v>
       </c>
       <c r="K18" t="n">
-        <v>26.14</v>
+        <v>32.2</v>
       </c>
       <c r="L18" t="n">
-        <v>26.14</v>
+        <v>33.03</v>
       </c>
       <c r="M18" t="n">
-        <v>26.14</v>
+        <v>33.88</v>
       </c>
       <c r="N18" t="n">
-        <v>26.14</v>
+        <v>34.73</v>
       </c>
       <c r="O18" t="n">
-        <v>26.14</v>
+        <v>35.59</v>
       </c>
       <c r="P18" t="n">
-        <v>26.14</v>
+        <v>36.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>26.14</v>
+        <v>37.33</v>
       </c>
       <c r="R18" t="n">
-        <v>26.14</v>
+        <v>38.21</v>
       </c>
       <c r="S18" t="n">
-        <v>26.14</v>
+        <v>39.09</v>
       </c>
       <c r="T18" t="n">
-        <v>26.14</v>
+        <v>39.98</v>
       </c>
       <c r="U18" t="n">
-        <v>26.14</v>
+        <v>40.88</v>
       </c>
       <c r="V18" t="n">
-        <v>26.2</v>
+        <v>41.79</v>
       </c>
       <c r="W18" t="n">
-        <v>26.26</v>
+        <v>42.7</v>
       </c>
       <c r="X18" t="n">
-        <v>26.32</v>
+        <v>43.62</v>
       </c>
       <c r="Y18" t="n">
-        <v>26.39</v>
+        <v>44.55</v>
       </c>
       <c r="Z18" t="n">
-        <v>26.45</v>
+        <v>45.48</v>
       </c>
       <c r="AA18" t="n">
-        <v>28.47</v>
+        <v>46.42</v>
       </c>
       <c r="AB18" t="n">
-        <v>30.49</v>
+        <v>47.37</v>
       </c>
       <c r="AC18" t="n">
-        <v>32.51</v>
+        <v>48.32</v>
       </c>
       <c r="AD18" t="n">
-        <v>34.53</v>
+        <v>49.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>36.56</v>
+        <v>50.25</v>
       </c>
       <c r="AF18" t="n">
-        <v>38.8</v>
+        <v>51.22</v>
       </c>
       <c r="AG18" t="n">
-        <v>41.05</v>
+        <v>52.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>43.29</v>
+        <v>53.19</v>
       </c>
       <c r="AI18" t="n">
-        <v>45.54</v>
+        <v>54.18</v>
       </c>
       <c r="AJ18" t="n">
-        <v>47.78</v>
+        <v>55.18</v>
       </c>
     </row>
     <row r="19">
@@ -2858,88 +2858,212 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>48.9</v>
+        <v>50.51</v>
       </c>
       <c r="J19" t="n">
-        <v>37.48</v>
+        <v>40.18</v>
       </c>
       <c r="K19" t="n">
-        <v>40.7</v>
+        <v>44.74</v>
       </c>
       <c r="L19" t="n">
-        <v>40.7</v>
+        <v>46.09</v>
       </c>
       <c r="M19" t="n">
-        <v>40.7</v>
+        <v>47.44</v>
       </c>
       <c r="N19" t="n">
-        <v>40.7</v>
+        <v>48.81</v>
       </c>
       <c r="O19" t="n">
-        <v>40.7</v>
+        <v>50.19</v>
       </c>
       <c r="P19" t="n">
-        <v>40.7</v>
+        <v>51.59</v>
       </c>
       <c r="Q19" t="n">
-        <v>41.15</v>
+        <v>52.99</v>
       </c>
       <c r="R19" t="n">
-        <v>41.61</v>
+        <v>54.4</v>
       </c>
       <c r="S19" t="n">
-        <v>42.07</v>
+        <v>55.83</v>
       </c>
       <c r="T19" t="n">
-        <v>42.52</v>
+        <v>57.26</v>
       </c>
       <c r="U19" t="n">
-        <v>42.98</v>
+        <v>58.71</v>
       </c>
       <c r="V19" t="n">
-        <v>43.78</v>
+        <v>60.16</v>
       </c>
       <c r="W19" t="n">
-        <v>44.57</v>
+        <v>61.63</v>
       </c>
       <c r="X19" t="n">
-        <v>45.37</v>
+        <v>63.11</v>
       </c>
       <c r="Y19" t="n">
-        <v>46.17</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="Z19" t="n">
-        <v>46.97</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="AA19" t="n">
-        <v>47.81</v>
+        <v>67.61</v>
       </c>
       <c r="AB19" t="n">
-        <v>48.64</v>
+        <v>69.14</v>
       </c>
       <c r="AC19" t="n">
-        <v>49.48</v>
+        <v>70.67</v>
       </c>
       <c r="AD19" t="n">
-        <v>50.31</v>
+        <v>72.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>51.15</v>
+        <v>73.77</v>
       </c>
       <c r="AF19" t="n">
-        <v>52</v>
+        <v>75.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>52.85</v>
+        <v>76.91</v>
       </c>
       <c r="AH19" t="n">
-        <v>53.7</v>
+        <v>78.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>54.54</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="AJ19" t="n">
-        <v>55.39</v>
+        <v>81.70999999999999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ELCHTIXX03</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Output demand of dispatch-ready in Haiti</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>not needed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>not needed</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>not needed</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>User defined</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>

--- a/t1_confection/A1_Outputs/A1_Outputs_NDC+ELC/A-O_Demand.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_NDC+ELC/A-O_Demand.xlsx
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ20"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.85546875" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -750,88 +750,88 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>524.49</v>
+        <v>555.91</v>
       </c>
       <c r="J2" t="n">
-        <v>506.39</v>
+        <v>555.91</v>
       </c>
       <c r="K2" t="n">
-        <v>512</v>
+        <v>555.91</v>
       </c>
       <c r="L2" t="n">
-        <v>518.55</v>
+        <v>567.9</v>
       </c>
       <c r="M2" t="n">
-        <v>525.15</v>
+        <v>579.88</v>
       </c>
       <c r="N2" t="n">
-        <v>531.79</v>
+        <v>591.87</v>
       </c>
       <c r="O2" t="n">
-        <v>538.48</v>
+        <v>603.85</v>
       </c>
       <c r="P2" t="n">
-        <v>545.2</v>
+        <v>615.83</v>
       </c>
       <c r="Q2" t="n">
-        <v>551.96</v>
+        <v>630.22</v>
       </c>
       <c r="R2" t="n">
-        <v>558.77</v>
+        <v>644.61</v>
       </c>
       <c r="S2" t="n">
-        <v>565.62</v>
+        <v>659</v>
       </c>
       <c r="T2" t="n">
-        <v>572.5</v>
+        <v>673.38</v>
       </c>
       <c r="U2" t="n">
-        <v>579.4299999999999</v>
+        <v>687.77</v>
       </c>
       <c r="V2" t="n">
-        <v>586.4</v>
+        <v>703</v>
       </c>
       <c r="W2" t="n">
-        <v>593.42</v>
+        <v>718.23</v>
       </c>
       <c r="X2" t="n">
-        <v>600.47</v>
+        <v>733.46</v>
       </c>
       <c r="Y2" t="n">
-        <v>607.5700000000001</v>
+        <v>748.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>614.7</v>
+        <v>763.9299999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>621.88</v>
+        <v>778.8099999999999</v>
       </c>
       <c r="AB2" t="n">
-        <v>629.1</v>
+        <v>793.6900000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>636.36</v>
+        <v>808.58</v>
       </c>
       <c r="AD2" t="n">
-        <v>643.66</v>
+        <v>823.46</v>
       </c>
       <c r="AE2" t="n">
-        <v>651</v>
+        <v>838.34</v>
       </c>
       <c r="AF2" t="n">
-        <v>658.38</v>
+        <v>853.52</v>
       </c>
       <c r="AG2" t="n">
-        <v>665.8099999999999</v>
+        <v>868.7</v>
       </c>
       <c r="AH2" t="n">
-        <v>673.28</v>
+        <v>883.88</v>
       </c>
       <c r="AI2" t="n">
-        <v>680.78</v>
+        <v>899.0599999999999</v>
       </c>
       <c r="AJ2" t="n">
-        <v>688.33</v>
+        <v>914.23</v>
       </c>
     </row>
     <row r="3">
@@ -874,88 +874,88 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>42.81</v>
+        <v>48.49</v>
       </c>
       <c r="J3" t="n">
-        <v>45.15</v>
+        <v>50.57</v>
       </c>
       <c r="K3" t="n">
-        <v>48.63</v>
+        <v>52.65</v>
       </c>
       <c r="L3" t="n">
-        <v>51.65</v>
+        <v>55.07</v>
       </c>
       <c r="M3" t="n">
-        <v>54.69</v>
+        <v>57.49</v>
       </c>
       <c r="N3" t="n">
-        <v>57.77</v>
+        <v>59.92</v>
       </c>
       <c r="O3" t="n">
-        <v>60.87</v>
+        <v>62.34</v>
       </c>
       <c r="P3" t="n">
-        <v>64</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>67.15000000000001</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>70.34</v>
+        <v>70.16</v>
       </c>
       <c r="S3" t="n">
-        <v>73.55</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>76.79000000000001</v>
+        <v>75.55</v>
       </c>
       <c r="U3" t="n">
-        <v>80.05</v>
+        <v>78.25</v>
       </c>
       <c r="V3" t="n">
-        <v>83.34999999999999</v>
+        <v>81.34</v>
       </c>
       <c r="W3" t="n">
-        <v>86.67</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>90.02</v>
+        <v>87.52</v>
       </c>
       <c r="Y3" t="n">
-        <v>93.39</v>
+        <v>90.61</v>
       </c>
       <c r="Z3" t="n">
-        <v>96.8</v>
+        <v>93.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>100.23</v>
+        <v>97.23</v>
       </c>
       <c r="AB3" t="n">
-        <v>103.69</v>
+        <v>100.76</v>
       </c>
       <c r="AC3" t="n">
-        <v>107.17</v>
+        <v>104.29</v>
       </c>
       <c r="AD3" t="n">
-        <v>110.69</v>
+        <v>107.82</v>
       </c>
       <c r="AE3" t="n">
-        <v>114.23</v>
+        <v>111.35</v>
       </c>
       <c r="AF3" t="n">
-        <v>117.8</v>
+        <v>115.41</v>
       </c>
       <c r="AG3" t="n">
-        <v>121.39</v>
+        <v>119.46</v>
       </c>
       <c r="AH3" t="n">
-        <v>125.02</v>
+        <v>123.52</v>
       </c>
       <c r="AI3" t="n">
-        <v>128.67</v>
+        <v>127.58</v>
       </c>
       <c r="AJ3" t="n">
-        <v>132.35</v>
+        <v>131.63</v>
       </c>
     </row>
     <row r="4">
@@ -998,88 +998,88 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2599.63</v>
+        <v>2217.88</v>
       </c>
       <c r="J4" t="n">
-        <v>2637.58</v>
+        <v>2217.88</v>
       </c>
       <c r="K4" t="n">
-        <v>2732.79</v>
+        <v>2217.88</v>
       </c>
       <c r="L4" t="n">
-        <v>2802.48</v>
+        <v>2217.88</v>
       </c>
       <c r="M4" t="n">
-        <v>2872.73</v>
+        <v>2217.88</v>
       </c>
       <c r="N4" t="n">
-        <v>2943.54</v>
+        <v>2217.88</v>
       </c>
       <c r="O4" t="n">
-        <v>3014.9</v>
+        <v>2217.88</v>
       </c>
       <c r="P4" t="n">
-        <v>3086.83</v>
+        <v>2217.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>3159.31</v>
+        <v>2239.39</v>
       </c>
       <c r="R4" t="n">
-        <v>3232.35</v>
+        <v>2260.91</v>
       </c>
       <c r="S4" t="n">
-        <v>3305.95</v>
+        <v>2282.45</v>
       </c>
       <c r="T4" t="n">
-        <v>3380.11</v>
+        <v>2303.96</v>
       </c>
       <c r="U4" t="n">
-        <v>3454.82</v>
+        <v>2325.48</v>
       </c>
       <c r="V4" t="n">
-        <v>3530.09</v>
+        <v>2365.7</v>
       </c>
       <c r="W4" t="n">
-        <v>3605.93</v>
+        <v>2405.95</v>
       </c>
       <c r="X4" t="n">
-        <v>3682.32</v>
+        <v>2446.19</v>
       </c>
       <c r="Y4" t="n">
-        <v>3759.26</v>
+        <v>2486.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>3836.77</v>
+        <v>2526.68</v>
       </c>
       <c r="AA4" t="n">
-        <v>3914.84</v>
+        <v>2565.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>3993.46</v>
+        <v>2604.71</v>
       </c>
       <c r="AC4" t="n">
-        <v>4072.64</v>
+        <v>2643.73</v>
       </c>
       <c r="AD4" t="n">
-        <v>4152.38</v>
+        <v>2682.73</v>
       </c>
       <c r="AE4" t="n">
-        <v>4232.68</v>
+        <v>2721.76</v>
       </c>
       <c r="AF4" t="n">
-        <v>4313.54</v>
+        <v>2761.04</v>
       </c>
       <c r="AG4" t="n">
-        <v>4394.95</v>
+        <v>2800.31</v>
       </c>
       <c r="AH4" t="n">
-        <v>4476.92</v>
+        <v>2839.59</v>
       </c>
       <c r="AI4" t="n">
-        <v>4559.46</v>
+        <v>2878.87</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4642.54</v>
+        <v>2918.15</v>
       </c>
     </row>
     <row r="5">
@@ -1122,88 +1122,88 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3.87</v>
+        <v>14.87</v>
       </c>
       <c r="J5" t="n">
-        <v>4.12</v>
+        <v>14.87</v>
       </c>
       <c r="K5" t="n">
-        <v>4.39</v>
+        <v>14.87</v>
       </c>
       <c r="L5" t="n">
-        <v>4.66</v>
+        <v>14.87</v>
       </c>
       <c r="M5" t="n">
-        <v>4.94</v>
+        <v>14.87</v>
       </c>
       <c r="N5" t="n">
-        <v>5.21</v>
+        <v>14.87</v>
       </c>
       <c r="O5" t="n">
-        <v>5.49</v>
+        <v>14.87</v>
       </c>
       <c r="P5" t="n">
-        <v>5.77</v>
+        <v>14.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.06</v>
+        <v>14.87</v>
       </c>
       <c r="R5" t="n">
-        <v>6.34</v>
+        <v>14.87</v>
       </c>
       <c r="S5" t="n">
-        <v>6.63</v>
+        <v>14.87</v>
       </c>
       <c r="T5" t="n">
-        <v>6.92</v>
+        <v>14.87</v>
       </c>
       <c r="U5" t="n">
-        <v>7.22</v>
+        <v>14.87</v>
       </c>
       <c r="V5" t="n">
-        <v>7.51</v>
+        <v>14.87</v>
       </c>
       <c r="W5" t="n">
-        <v>7.81</v>
+        <v>14.87</v>
       </c>
       <c r="X5" t="n">
-        <v>8.109999999999999</v>
+        <v>14.87</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.42</v>
+        <v>14.87</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.720000000000001</v>
+        <v>14.87</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.029999999999999</v>
+        <v>14.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.34</v>
+        <v>14.88</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.65</v>
+        <v>14.89</v>
       </c>
       <c r="AD5" t="n">
-        <v>9.970000000000001</v>
+        <v>14.9</v>
       </c>
       <c r="AE5" t="n">
-        <v>10.29</v>
+        <v>14.9</v>
       </c>
       <c r="AF5" t="n">
-        <v>10.61</v>
+        <v>15.73</v>
       </c>
       <c r="AG5" t="n">
-        <v>10.93</v>
+        <v>16.55</v>
       </c>
       <c r="AH5" t="n">
-        <v>11.26</v>
+        <v>17.37</v>
       </c>
       <c r="AI5" t="n">
-        <v>11.59</v>
+        <v>18.19</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11.92</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="6">
@@ -1246,88 +1246,88 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>302.25</v>
+        <v>271.4</v>
       </c>
       <c r="J6" t="n">
-        <v>318.54</v>
+        <v>271.4</v>
       </c>
       <c r="K6" t="n">
-        <v>336.33</v>
+        <v>271.4</v>
       </c>
       <c r="L6" t="n">
-        <v>354.31</v>
+        <v>271.4</v>
       </c>
       <c r="M6" t="n">
-        <v>372.46</v>
+        <v>271.4</v>
       </c>
       <c r="N6" t="n">
-        <v>390.76</v>
+        <v>271.4</v>
       </c>
       <c r="O6" t="n">
-        <v>409.23</v>
+        <v>271.4</v>
       </c>
       <c r="P6" t="n">
-        <v>427.86</v>
+        <v>271.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>446.65</v>
+        <v>272.9</v>
       </c>
       <c r="R6" t="n">
-        <v>465.6</v>
+        <v>274.4</v>
       </c>
       <c r="S6" t="n">
-        <v>484.71</v>
+        <v>275.89</v>
       </c>
       <c r="T6" t="n">
-        <v>503.99</v>
+        <v>277.39</v>
       </c>
       <c r="U6" t="n">
-        <v>523.4299999999999</v>
+        <v>278.88</v>
       </c>
       <c r="V6" t="n">
-        <v>543.02</v>
+        <v>284.94</v>
       </c>
       <c r="W6" t="n">
-        <v>562.78</v>
+        <v>291</v>
       </c>
       <c r="X6" t="n">
-        <v>582.7</v>
+        <v>297.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>602.78</v>
+        <v>303.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>623.03</v>
+        <v>309.19</v>
       </c>
       <c r="AA6" t="n">
-        <v>643.4299999999999</v>
+        <v>315.49</v>
       </c>
       <c r="AB6" t="n">
-        <v>664</v>
+        <v>321.79</v>
       </c>
       <c r="AC6" t="n">
-        <v>684.73</v>
+        <v>328.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>705.62</v>
+        <v>334.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>726.67</v>
+        <v>340.71</v>
       </c>
       <c r="AF6" t="n">
-        <v>747.88</v>
+        <v>347</v>
       </c>
       <c r="AG6" t="n">
-        <v>769.25</v>
+        <v>353.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>790.79</v>
+        <v>359.58</v>
       </c>
       <c r="AI6" t="n">
-        <v>812.48</v>
+        <v>365.87</v>
       </c>
       <c r="AJ6" t="n">
-        <v>834.34</v>
+        <v>372.16</v>
       </c>
     </row>
     <row r="7">
@@ -1370,88 +1370,88 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>288.23</v>
+        <v>383.28</v>
       </c>
       <c r="J7" t="n">
-        <v>296.14</v>
+        <v>393.61</v>
       </c>
       <c r="K7" t="n">
-        <v>312.39</v>
+        <v>403.93</v>
       </c>
       <c r="L7" t="n">
-        <v>324.75</v>
+        <v>415.72</v>
       </c>
       <c r="M7" t="n">
-        <v>337.23</v>
+        <v>427.5</v>
       </c>
       <c r="N7" t="n">
-        <v>349.81</v>
+        <v>439.29</v>
       </c>
       <c r="O7" t="n">
-        <v>362.5</v>
+        <v>451.08</v>
       </c>
       <c r="P7" t="n">
-        <v>375.3</v>
+        <v>462.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>388.2</v>
+        <v>475.69</v>
       </c>
       <c r="R7" t="n">
-        <v>401.22</v>
+        <v>488.52</v>
       </c>
       <c r="S7" t="n">
-        <v>414.33</v>
+        <v>501.35</v>
       </c>
       <c r="T7" t="n">
-        <v>427.56</v>
+        <v>514.17</v>
       </c>
       <c r="U7" t="n">
-        <v>440.89</v>
+        <v>527</v>
       </c>
       <c r="V7" t="n">
-        <v>454.33</v>
+        <v>541.29</v>
       </c>
       <c r="W7" t="n">
-        <v>467.88</v>
+        <v>555.58</v>
       </c>
       <c r="X7" t="n">
-        <v>481.53</v>
+        <v>569.86</v>
       </c>
       <c r="Y7" t="n">
-        <v>495.29</v>
+        <v>584.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>509.16</v>
+        <v>598.4400000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>523.13</v>
+        <v>614</v>
       </c>
       <c r="AB7" t="n">
-        <v>537.21</v>
+        <v>629.5599999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>551.4</v>
+        <v>645.13</v>
       </c>
       <c r="AD7" t="n">
-        <v>565.7</v>
+        <v>660.6900000000001</v>
       </c>
       <c r="AE7" t="n">
-        <v>580.1</v>
+        <v>676.26</v>
       </c>
       <c r="AF7" t="n">
-        <v>594.61</v>
+        <v>692.9400000000001</v>
       </c>
       <c r="AG7" t="n">
-        <v>609.23</v>
+        <v>709.63</v>
       </c>
       <c r="AH7" t="n">
-        <v>623.95</v>
+        <v>726.3099999999999</v>
       </c>
       <c r="AI7" t="n">
-        <v>638.78</v>
+        <v>743</v>
       </c>
       <c r="AJ7" t="n">
-        <v>653.72</v>
+        <v>759.6799999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1494,88 +1494,88 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>44.28</v>
+        <v>45.41</v>
       </c>
       <c r="J8" t="n">
-        <v>44.68</v>
+        <v>47.7</v>
       </c>
       <c r="K8" t="n">
-        <v>43.8</v>
+        <v>50</v>
       </c>
       <c r="L8" t="n">
-        <v>44.92</v>
+        <v>52.7</v>
       </c>
       <c r="M8" t="n">
-        <v>46.04</v>
+        <v>55.41</v>
       </c>
       <c r="N8" t="n">
-        <v>47.18</v>
+        <v>58.11</v>
       </c>
       <c r="O8" t="n">
-        <v>48.32</v>
+        <v>60.82</v>
       </c>
       <c r="P8" t="n">
-        <v>49.48</v>
+        <v>63.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>50.64</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>51.81</v>
+        <v>69.45</v>
       </c>
       <c r="S8" t="n">
-        <v>52.99</v>
+        <v>72.41</v>
       </c>
       <c r="T8" t="n">
-        <v>54.18</v>
+        <v>75.37</v>
       </c>
       <c r="U8" t="n">
-        <v>55.38</v>
+        <v>78.33</v>
       </c>
       <c r="V8" t="n">
-        <v>56.58</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>57.8</v>
+        <v>85.03</v>
       </c>
       <c r="X8" t="n">
-        <v>59.02</v>
+        <v>88.37</v>
       </c>
       <c r="Y8" t="n">
-        <v>60.26</v>
+        <v>91.72</v>
       </c>
       <c r="Z8" t="n">
-        <v>61.5</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>62.75</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>64.01000000000001</v>
+        <v>102.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>65.28</v>
+        <v>106</v>
       </c>
       <c r="AD8" t="n">
-        <v>66.56</v>
+        <v>109.64</v>
       </c>
       <c r="AE8" t="n">
-        <v>67.84</v>
+        <v>113.29</v>
       </c>
       <c r="AF8" t="n">
-        <v>69.14</v>
+        <v>117.13</v>
       </c>
       <c r="AG8" t="n">
-        <v>70.44</v>
+        <v>120.96</v>
       </c>
       <c r="AH8" t="n">
-        <v>71.75</v>
+        <v>124.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>73.08</v>
+        <v>128.64</v>
       </c>
       <c r="AJ8" t="n">
-        <v>74.41</v>
+        <v>132.47</v>
       </c>
     </row>
     <row r="9">
@@ -1618,88 +1618,88 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>86.09</v>
+        <v>66.8</v>
       </c>
       <c r="J9" t="n">
-        <v>89.09999999999999</v>
+        <v>66.92</v>
       </c>
       <c r="K9" t="n">
-        <v>92.56999999999999</v>
+        <v>67.03</v>
       </c>
       <c r="L9" t="n">
-        <v>96.08</v>
+        <v>71.7</v>
       </c>
       <c r="M9" t="n">
-        <v>99.61</v>
+        <v>76.37</v>
       </c>
       <c r="N9" t="n">
-        <v>103.17</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>106.77</v>
+        <v>85.7</v>
       </c>
       <c r="P9" t="n">
-        <v>110.39</v>
+        <v>90.37</v>
       </c>
       <c r="Q9" t="n">
-        <v>114.05</v>
+        <v>95.44</v>
       </c>
       <c r="R9" t="n">
-        <v>117.73</v>
+        <v>100.51</v>
       </c>
       <c r="S9" t="n">
-        <v>121.44</v>
+        <v>105.58</v>
       </c>
       <c r="T9" t="n">
-        <v>125.19</v>
+        <v>110.65</v>
       </c>
       <c r="U9" t="n">
-        <v>128.96</v>
+        <v>115.72</v>
       </c>
       <c r="V9" t="n">
-        <v>132.77</v>
+        <v>121.48</v>
       </c>
       <c r="W9" t="n">
-        <v>136.6</v>
+        <v>127.23</v>
       </c>
       <c r="X9" t="n">
-        <v>140.47</v>
+        <v>132.98</v>
       </c>
       <c r="Y9" t="n">
-        <v>144.36</v>
+        <v>138.73</v>
       </c>
       <c r="Z9" t="n">
-        <v>148.29</v>
+        <v>144.49</v>
       </c>
       <c r="AA9" t="n">
-        <v>152.25</v>
+        <v>150.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>156.23</v>
+        <v>157.18</v>
       </c>
       <c r="AC9" t="n">
-        <v>160.25</v>
+        <v>163.53</v>
       </c>
       <c r="AD9" t="n">
-        <v>164.29</v>
+        <v>169.88</v>
       </c>
       <c r="AE9" t="n">
-        <v>168.37</v>
+        <v>176.23</v>
       </c>
       <c r="AF9" t="n">
-        <v>172.48</v>
+        <v>183.07</v>
       </c>
       <c r="AG9" t="n">
-        <v>176.61</v>
+        <v>189.91</v>
       </c>
       <c r="AH9" t="n">
-        <v>180.78</v>
+        <v>196.75</v>
       </c>
       <c r="AI9" t="n">
-        <v>184.98</v>
+        <v>203.59</v>
       </c>
       <c r="AJ9" t="n">
-        <v>189.2</v>
+        <v>210.44</v>
       </c>
     </row>
     <row r="10">
@@ -1742,88 +1742,88 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>129.57</v>
+        <v>97.41</v>
       </c>
       <c r="J10" t="n">
-        <v>137.75</v>
+        <v>98.33</v>
       </c>
       <c r="K10" t="n">
-        <v>140.3</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>146.86</v>
+        <v>102.44</v>
       </c>
       <c r="M10" t="n">
-        <v>153.47</v>
+        <v>105.63</v>
       </c>
       <c r="N10" t="n">
-        <v>160.15</v>
+        <v>108.81</v>
       </c>
       <c r="O10" t="n">
-        <v>166.88</v>
+        <v>111.99</v>
       </c>
       <c r="P10" t="n">
-        <v>173.67</v>
+        <v>115.18</v>
       </c>
       <c r="Q10" t="n">
-        <v>180.51</v>
+        <v>118.64</v>
       </c>
       <c r="R10" t="n">
-        <v>187.42</v>
+        <v>122.11</v>
       </c>
       <c r="S10" t="n">
-        <v>194.38</v>
+        <v>125.58</v>
       </c>
       <c r="T10" t="n">
-        <v>201.41</v>
+        <v>129.04</v>
       </c>
       <c r="U10" t="n">
-        <v>208.49</v>
+        <v>132.51</v>
       </c>
       <c r="V10" t="n">
-        <v>215.62</v>
+        <v>136.51</v>
       </c>
       <c r="W10" t="n">
-        <v>222.82</v>
+        <v>140.51</v>
       </c>
       <c r="X10" t="n">
-        <v>230.08</v>
+        <v>144.51</v>
       </c>
       <c r="Y10" t="n">
-        <v>237.39</v>
+        <v>148.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>244.76</v>
+        <v>152.52</v>
       </c>
       <c r="AA10" t="n">
-        <v>252.19</v>
+        <v>157.16</v>
       </c>
       <c r="AB10" t="n">
-        <v>259.67</v>
+        <v>161.81</v>
       </c>
       <c r="AC10" t="n">
-        <v>267.22</v>
+        <v>166.46</v>
       </c>
       <c r="AD10" t="n">
-        <v>274.82</v>
+        <v>171.1</v>
       </c>
       <c r="AE10" t="n">
-        <v>282.48</v>
+        <v>175.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>290.2</v>
+        <v>181.04</v>
       </c>
       <c r="AG10" t="n">
-        <v>297.98</v>
+        <v>186.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>305.81</v>
+        <v>191.61</v>
       </c>
       <c r="AI10" t="n">
-        <v>313.7</v>
+        <v>196.9</v>
       </c>
       <c r="AJ10" t="n">
-        <v>321.65</v>
+        <v>202.19</v>
       </c>
     </row>
     <row r="11">
@@ -1866,88 +1866,88 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>47.17</v>
+        <v>38.02</v>
       </c>
       <c r="J11" t="n">
-        <v>48.54</v>
+        <v>38.02</v>
       </c>
       <c r="K11" t="n">
-        <v>48.77</v>
+        <v>38.02</v>
       </c>
       <c r="L11" t="n">
-        <v>50.55</v>
+        <v>38.02</v>
       </c>
       <c r="M11" t="n">
-        <v>52.35</v>
+        <v>38.02</v>
       </c>
       <c r="N11" t="n">
-        <v>54.16</v>
+        <v>38.02</v>
       </c>
       <c r="O11" t="n">
-        <v>55.99</v>
+        <v>38.02</v>
       </c>
       <c r="P11" t="n">
-        <v>57.83</v>
+        <v>38.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>59.69</v>
+        <v>38.02</v>
       </c>
       <c r="R11" t="n">
-        <v>61.57</v>
+        <v>38.02</v>
       </c>
       <c r="S11" t="n">
-        <v>63.45</v>
+        <v>38.02</v>
       </c>
       <c r="T11" t="n">
-        <v>65.36</v>
+        <v>38.02</v>
       </c>
       <c r="U11" t="n">
-        <v>67.28</v>
+        <v>38.02</v>
       </c>
       <c r="V11" t="n">
-        <v>69.20999999999999</v>
+        <v>40.54</v>
       </c>
       <c r="W11" t="n">
-        <v>71.16</v>
+        <v>43.06</v>
       </c>
       <c r="X11" t="n">
-        <v>73.13</v>
+        <v>45.58</v>
       </c>
       <c r="Y11" t="n">
-        <v>75.11</v>
+        <v>48.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>77.11</v>
+        <v>50.61</v>
       </c>
       <c r="AA11" t="n">
-        <v>79.12</v>
+        <v>59</v>
       </c>
       <c r="AB11" t="n">
-        <v>81.15000000000001</v>
+        <v>67.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>83.19</v>
+        <v>75.77</v>
       </c>
       <c r="AD11" t="n">
-        <v>85.25</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="AE11" t="n">
-        <v>87.31999999999999</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="AF11" t="n">
-        <v>89.41</v>
+        <v>103.19</v>
       </c>
       <c r="AG11" t="n">
-        <v>91.51000000000001</v>
+        <v>113.85</v>
       </c>
       <c r="AH11" t="n">
-        <v>93.63</v>
+        <v>124.51</v>
       </c>
       <c r="AI11" t="n">
-        <v>95.76000000000001</v>
+        <v>135.16</v>
       </c>
       <c r="AJ11" t="n">
-        <v>97.91</v>
+        <v>145.82</v>
       </c>
     </row>
     <row r="12">
@@ -1990,88 +1990,88 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>43.14</v>
+        <v>32.8</v>
       </c>
       <c r="J12" t="n">
-        <v>44.46</v>
+        <v>32.8</v>
       </c>
       <c r="K12" t="n">
-        <v>46.16</v>
+        <v>32.8</v>
       </c>
       <c r="L12" t="n">
-        <v>47.71</v>
+        <v>32.8</v>
       </c>
       <c r="M12" t="n">
-        <v>49.26</v>
+        <v>32.8</v>
       </c>
       <c r="N12" t="n">
-        <v>50.83</v>
+        <v>32.8</v>
       </c>
       <c r="O12" t="n">
-        <v>52.42</v>
+        <v>32.8</v>
       </c>
       <c r="P12" t="n">
-        <v>54.01</v>
+        <v>32.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>55.62</v>
+        <v>32.8</v>
       </c>
       <c r="R12" t="n">
-        <v>57.25</v>
+        <v>32.8</v>
       </c>
       <c r="S12" t="n">
-        <v>58.88</v>
+        <v>32.8</v>
       </c>
       <c r="T12" t="n">
-        <v>60.53</v>
+        <v>32.8</v>
       </c>
       <c r="U12" t="n">
-        <v>62.19</v>
+        <v>32.8</v>
       </c>
       <c r="V12" t="n">
-        <v>63.87</v>
+        <v>32.8</v>
       </c>
       <c r="W12" t="n">
-        <v>65.55</v>
+        <v>32.8</v>
       </c>
       <c r="X12" t="n">
-        <v>67.25</v>
+        <v>32.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>68.97</v>
+        <v>32.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>70.69</v>
+        <v>32.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>72.43000000000001</v>
+        <v>32.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>74.19</v>
+        <v>32.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>75.95</v>
+        <v>32.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>77.73</v>
+        <v>32.8</v>
       </c>
       <c r="AE12" t="n">
-        <v>79.52</v>
+        <v>32.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>81.33</v>
+        <v>37.49</v>
       </c>
       <c r="AG12" t="n">
-        <v>83.15000000000001</v>
+        <v>42.19</v>
       </c>
       <c r="AH12" t="n">
-        <v>84.98</v>
+        <v>46.89</v>
       </c>
       <c r="AI12" t="n">
-        <v>86.81999999999999</v>
+        <v>51.59</v>
       </c>
       <c r="AJ12" t="n">
-        <v>88.68000000000001</v>
+        <v>56.28</v>
       </c>
     </row>
     <row r="13">
@@ -2114,88 +2114,88 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1241.42</v>
+        <v>1212.64</v>
       </c>
       <c r="J13" t="n">
-        <v>1279.49</v>
+        <v>1244.28</v>
       </c>
       <c r="K13" t="n">
-        <v>1324.32</v>
+        <v>1275.93</v>
       </c>
       <c r="L13" t="n">
-        <v>1368.73</v>
+        <v>1340.26</v>
       </c>
       <c r="M13" t="n">
-        <v>1413.51</v>
+        <v>1404.59</v>
       </c>
       <c r="N13" t="n">
-        <v>1458.67</v>
+        <v>1468.93</v>
       </c>
       <c r="O13" t="n">
-        <v>1504.2</v>
+        <v>1533.26</v>
       </c>
       <c r="P13" t="n">
-        <v>1550.1</v>
+        <v>1597.59</v>
       </c>
       <c r="Q13" t="n">
-        <v>1596.38</v>
+        <v>1668.19</v>
       </c>
       <c r="R13" t="n">
-        <v>1643.03</v>
+        <v>1738.78</v>
       </c>
       <c r="S13" t="n">
-        <v>1690.06</v>
+        <v>1809.38</v>
       </c>
       <c r="T13" t="n">
-        <v>1737.46</v>
+        <v>1879.97</v>
       </c>
       <c r="U13" t="n">
-        <v>1785.24</v>
+        <v>1950.57</v>
       </c>
       <c r="V13" t="n">
-        <v>1833.39</v>
+        <v>2027.16</v>
       </c>
       <c r="W13" t="n">
-        <v>1881.91</v>
+        <v>2103.75</v>
       </c>
       <c r="X13" t="n">
-        <v>1930.81</v>
+        <v>2180.34</v>
       </c>
       <c r="Y13" t="n">
-        <v>1980.09</v>
+        <v>2256.94</v>
       </c>
       <c r="Z13" t="n">
-        <v>2029.73</v>
+        <v>2333.53</v>
       </c>
       <c r="AA13" t="n">
-        <v>2079.75</v>
+        <v>2418.53</v>
       </c>
       <c r="AB13" t="n">
-        <v>2130.15</v>
+        <v>2503.54</v>
       </c>
       <c r="AC13" t="n">
-        <v>2180.92</v>
+        <v>2588.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>2232.06</v>
+        <v>2673.56</v>
       </c>
       <c r="AE13" t="n">
-        <v>2283.58</v>
+        <v>2758.57</v>
       </c>
       <c r="AF13" t="n">
-        <v>2335.47</v>
+        <v>2853.23</v>
       </c>
       <c r="AG13" t="n">
-        <v>2387.74</v>
+        <v>2947.89</v>
       </c>
       <c r="AH13" t="n">
-        <v>2440.38</v>
+        <v>3042.55</v>
       </c>
       <c r="AI13" t="n">
-        <v>2493.4</v>
+        <v>3137.21</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2546.79</v>
+        <v>3231.87</v>
       </c>
     </row>
     <row r="14">
@@ -2238,88 +2238,88 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>20.33</v>
+        <v>16.52</v>
       </c>
       <c r="J14" t="n">
-        <v>21.29</v>
+        <v>16.52</v>
       </c>
       <c r="K14" t="n">
-        <v>22.54</v>
+        <v>16.52</v>
       </c>
       <c r="L14" t="n">
-        <v>23.44</v>
+        <v>16.52</v>
       </c>
       <c r="M14" t="n">
-        <v>24.34</v>
+        <v>16.52</v>
       </c>
       <c r="N14" t="n">
-        <v>25.26</v>
+        <v>16.52</v>
       </c>
       <c r="O14" t="n">
-        <v>26.18</v>
+        <v>16.52</v>
       </c>
       <c r="P14" t="n">
-        <v>27.11</v>
+        <v>16.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>28.04</v>
+        <v>16.52</v>
       </c>
       <c r="R14" t="n">
-        <v>28.99</v>
+        <v>16.52</v>
       </c>
       <c r="S14" t="n">
-        <v>29.94</v>
+        <v>16.52</v>
       </c>
       <c r="T14" t="n">
-        <v>30.9</v>
+        <v>16.52</v>
       </c>
       <c r="U14" t="n">
-        <v>31.87</v>
+        <v>16.52</v>
       </c>
       <c r="V14" t="n">
-        <v>32.85</v>
+        <v>16.52</v>
       </c>
       <c r="W14" t="n">
-        <v>33.83</v>
+        <v>16.52</v>
       </c>
       <c r="X14" t="n">
-        <v>34.83</v>
+        <v>16.52</v>
       </c>
       <c r="Y14" t="n">
-        <v>35.83</v>
+        <v>16.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>36.84</v>
+        <v>16.52</v>
       </c>
       <c r="AA14" t="n">
-        <v>37.85</v>
+        <v>16.66</v>
       </c>
       <c r="AB14" t="n">
-        <v>38.88</v>
+        <v>16.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>39.91</v>
+        <v>16.94</v>
       </c>
       <c r="AD14" t="n">
-        <v>40.95</v>
+        <v>17.08</v>
       </c>
       <c r="AE14" t="n">
-        <v>42</v>
+        <v>17.22</v>
       </c>
       <c r="AF14" t="n">
-        <v>43.05</v>
+        <v>20.52</v>
       </c>
       <c r="AG14" t="n">
-        <v>44.12</v>
+        <v>23.82</v>
       </c>
       <c r="AH14" t="n">
-        <v>45.19</v>
+        <v>27.12</v>
       </c>
       <c r="AI14" t="n">
-        <v>46.27</v>
+        <v>30.41</v>
       </c>
       <c r="AJ14" t="n">
-        <v>47.36</v>
+        <v>33.71</v>
       </c>
     </row>
     <row r="15">
@@ -2362,88 +2362,88 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>51.79</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>52.92</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>56.46</v>
+        <v>79.62</v>
       </c>
       <c r="L15" t="n">
-        <v>59.32</v>
+        <v>84.13</v>
       </c>
       <c r="M15" t="n">
-        <v>62.2</v>
+        <v>88.63</v>
       </c>
       <c r="N15" t="n">
-        <v>65.11</v>
+        <v>93.14</v>
       </c>
       <c r="O15" t="n">
-        <v>68.05</v>
+        <v>97.64</v>
       </c>
       <c r="P15" t="n">
-        <v>71.01000000000001</v>
+        <v>102.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>74</v>
+        <v>106.85</v>
       </c>
       <c r="R15" t="n">
-        <v>77.01000000000001</v>
+        <v>111.55</v>
       </c>
       <c r="S15" t="n">
-        <v>80.05</v>
+        <v>116.26</v>
       </c>
       <c r="T15" t="n">
-        <v>83.11</v>
+        <v>120.96</v>
       </c>
       <c r="U15" t="n">
-        <v>86.2</v>
+        <v>125.66</v>
       </c>
       <c r="V15" t="n">
-        <v>89.31999999999999</v>
+        <v>130.6</v>
       </c>
       <c r="W15" t="n">
-        <v>92.45999999999999</v>
+        <v>135.55</v>
       </c>
       <c r="X15" t="n">
-        <v>95.62</v>
+        <v>140.49</v>
       </c>
       <c r="Y15" t="n">
-        <v>98.81999999999999</v>
+        <v>145.43</v>
       </c>
       <c r="Z15" t="n">
-        <v>102.03</v>
+        <v>150.37</v>
       </c>
       <c r="AA15" t="n">
-        <v>105.28</v>
+        <v>155.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>108.54</v>
+        <v>161.04</v>
       </c>
       <c r="AC15" t="n">
-        <v>111.84</v>
+        <v>166.37</v>
       </c>
       <c r="AD15" t="n">
-        <v>115.15</v>
+        <v>171.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>118.5</v>
+        <v>177.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>121.87</v>
+        <v>182.55</v>
       </c>
       <c r="AG15" t="n">
-        <v>125.26</v>
+        <v>188.07</v>
       </c>
       <c r="AH15" t="n">
-        <v>128.68</v>
+        <v>193.58</v>
       </c>
       <c r="AI15" t="n">
-        <v>132.13</v>
+        <v>199.1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>135.6</v>
+        <v>204.62</v>
       </c>
     </row>
     <row r="16">
@@ -2486,88 +2486,88 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>223.04</v>
+        <v>257.51</v>
       </c>
       <c r="J16" t="n">
-        <v>233.01</v>
+        <v>266.64</v>
       </c>
       <c r="K16" t="n">
-        <v>243.77</v>
+        <v>275.78</v>
       </c>
       <c r="L16" t="n">
-        <v>254.64</v>
+        <v>284.8</v>
       </c>
       <c r="M16" t="n">
-        <v>265.61</v>
+        <v>293.82</v>
       </c>
       <c r="N16" t="n">
-        <v>276.67</v>
+        <v>302.84</v>
       </c>
       <c r="O16" t="n">
-        <v>287.83</v>
+        <v>311.86</v>
       </c>
       <c r="P16" t="n">
-        <v>299.09</v>
+        <v>320.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>310.44</v>
+        <v>330</v>
       </c>
       <c r="R16" t="n">
-        <v>321.88</v>
+        <v>339.12</v>
       </c>
       <c r="S16" t="n">
-        <v>333.42</v>
+        <v>348.24</v>
       </c>
       <c r="T16" t="n">
-        <v>345.06</v>
+        <v>357.36</v>
       </c>
       <c r="U16" t="n">
-        <v>356.79</v>
+        <v>366.48</v>
       </c>
       <c r="V16" t="n">
-        <v>368.62</v>
+        <v>376.05</v>
       </c>
       <c r="W16" t="n">
-        <v>380.55</v>
+        <v>385.63</v>
       </c>
       <c r="X16" t="n">
-        <v>392.57</v>
+        <v>395.21</v>
       </c>
       <c r="Y16" t="n">
-        <v>404.68</v>
+        <v>404.78</v>
       </c>
       <c r="Z16" t="n">
-        <v>416.89</v>
+        <v>414.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>429.2</v>
+        <v>424.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>441.6</v>
+        <v>434.36</v>
       </c>
       <c r="AC16" t="n">
-        <v>454.1</v>
+        <v>444.37</v>
       </c>
       <c r="AD16" t="n">
-        <v>466.69</v>
+        <v>454.37</v>
       </c>
       <c r="AE16" t="n">
-        <v>479.38</v>
+        <v>464.37</v>
       </c>
       <c r="AF16" t="n">
-        <v>492.17</v>
+        <v>474.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>505.05</v>
+        <v>484.93</v>
       </c>
       <c r="AH16" t="n">
-        <v>518.02</v>
+        <v>495.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>531.1</v>
+        <v>505.48</v>
       </c>
       <c r="AJ16" t="n">
-        <v>544.26</v>
+        <v>515.76</v>
       </c>
     </row>
     <row r="17">
@@ -2610,88 +2610,88 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>81.55</v>
+        <v>52.63</v>
       </c>
       <c r="J17" t="n">
-        <v>145.53</v>
+        <v>52.63</v>
       </c>
       <c r="K17" t="n">
-        <v>129.94</v>
+        <v>52.63</v>
       </c>
       <c r="L17" t="n">
-        <v>143.32</v>
+        <v>52.63</v>
       </c>
       <c r="M17" t="n">
-        <v>156.83</v>
+        <v>52.63</v>
       </c>
       <c r="N17" t="n">
-        <v>170.45</v>
+        <v>52.63</v>
       </c>
       <c r="O17" t="n">
-        <v>184.2</v>
+        <v>52.63</v>
       </c>
       <c r="P17" t="n">
-        <v>198.07</v>
+        <v>52.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>212.06</v>
+        <v>52.63</v>
       </c>
       <c r="R17" t="n">
-        <v>226.17</v>
+        <v>52.63</v>
       </c>
       <c r="S17" t="n">
-        <v>240.4</v>
+        <v>52.63</v>
       </c>
       <c r="T17" t="n">
-        <v>254.76</v>
+        <v>52.63</v>
       </c>
       <c r="U17" t="n">
-        <v>269.23</v>
+        <v>52.63</v>
       </c>
       <c r="V17" t="n">
-        <v>283.83</v>
+        <v>54.53</v>
       </c>
       <c r="W17" t="n">
-        <v>298.55</v>
+        <v>56.44</v>
       </c>
       <c r="X17" t="n">
-        <v>313.4</v>
+        <v>58.34</v>
       </c>
       <c r="Y17" t="n">
-        <v>328.36</v>
+        <v>60.24</v>
       </c>
       <c r="Z17" t="n">
-        <v>343.45</v>
+        <v>62.14</v>
       </c>
       <c r="AA17" t="n">
-        <v>358.66</v>
+        <v>64.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>373.99</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>389.44</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>405.01</v>
+        <v>72.38</v>
       </c>
       <c r="AE17" t="n">
-        <v>420.71</v>
+        <v>74.94</v>
       </c>
       <c r="AF17" t="n">
-        <v>436.53</v>
+        <v>77.86</v>
       </c>
       <c r="AG17" t="n">
-        <v>452.47</v>
+        <v>80.78</v>
       </c>
       <c r="AH17" t="n">
-        <v>468.53</v>
+        <v>83.7</v>
       </c>
       <c r="AI17" t="n">
-        <v>484.71</v>
+        <v>86.62</v>
       </c>
       <c r="AJ17" t="n">
-        <v>501.02</v>
+        <v>89.54000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -2734,88 +2734,88 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>27.94</v>
+        <v>24.8</v>
       </c>
       <c r="J18" t="n">
-        <v>29.86</v>
+        <v>24.8</v>
       </c>
       <c r="K18" t="n">
-        <v>32.2</v>
+        <v>24.8</v>
       </c>
       <c r="L18" t="n">
-        <v>33.03</v>
+        <v>24.8</v>
       </c>
       <c r="M18" t="n">
-        <v>33.88</v>
+        <v>24.8</v>
       </c>
       <c r="N18" t="n">
-        <v>34.73</v>
+        <v>24.8</v>
       </c>
       <c r="O18" t="n">
-        <v>35.59</v>
+        <v>24.8</v>
       </c>
       <c r="P18" t="n">
-        <v>36.45</v>
+        <v>24.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>37.33</v>
+        <v>24.8</v>
       </c>
       <c r="R18" t="n">
-        <v>38.21</v>
+        <v>24.8</v>
       </c>
       <c r="S18" t="n">
-        <v>39.09</v>
+        <v>24.8</v>
       </c>
       <c r="T18" t="n">
-        <v>39.98</v>
+        <v>24.8</v>
       </c>
       <c r="U18" t="n">
-        <v>40.88</v>
+        <v>24.8</v>
       </c>
       <c r="V18" t="n">
-        <v>41.79</v>
+        <v>24.86</v>
       </c>
       <c r="W18" t="n">
-        <v>42.7</v>
+        <v>24.92</v>
       </c>
       <c r="X18" t="n">
-        <v>43.62</v>
+        <v>24.98</v>
       </c>
       <c r="Y18" t="n">
-        <v>44.55</v>
+        <v>25.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>45.48</v>
+        <v>25.11</v>
       </c>
       <c r="AA18" t="n">
-        <v>46.42</v>
+        <v>27.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>47.37</v>
+        <v>29.15</v>
       </c>
       <c r="AC18" t="n">
-        <v>48.32</v>
+        <v>31.17</v>
       </c>
       <c r="AD18" t="n">
-        <v>49.28</v>
+        <v>33.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>50.25</v>
+        <v>35.22</v>
       </c>
       <c r="AF18" t="n">
-        <v>51.22</v>
+        <v>37.46</v>
       </c>
       <c r="AG18" t="n">
-        <v>52.2</v>
+        <v>39.71</v>
       </c>
       <c r="AH18" t="n">
-        <v>53.19</v>
+        <v>41.95</v>
       </c>
       <c r="AI18" t="n">
-        <v>54.18</v>
+        <v>44.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>55.18</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="19">
@@ -2858,212 +2858,88 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>50.51</v>
+        <v>44.75</v>
       </c>
       <c r="J19" t="n">
-        <v>40.18</v>
+        <v>44.75</v>
       </c>
       <c r="K19" t="n">
-        <v>44.74</v>
+        <v>44.75</v>
       </c>
       <c r="L19" t="n">
-        <v>46.09</v>
+        <v>44.75</v>
       </c>
       <c r="M19" t="n">
-        <v>47.44</v>
+        <v>44.75</v>
       </c>
       <c r="N19" t="n">
-        <v>48.81</v>
+        <v>44.75</v>
       </c>
       <c r="O19" t="n">
-        <v>50.19</v>
+        <v>44.75</v>
       </c>
       <c r="P19" t="n">
-        <v>51.59</v>
+        <v>44.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>52.99</v>
+        <v>45.2</v>
       </c>
       <c r="R19" t="n">
-        <v>54.4</v>
+        <v>45.66</v>
       </c>
       <c r="S19" t="n">
-        <v>55.83</v>
+        <v>46.12</v>
       </c>
       <c r="T19" t="n">
-        <v>57.26</v>
+        <v>46.57</v>
       </c>
       <c r="U19" t="n">
-        <v>58.71</v>
+        <v>47.03</v>
       </c>
       <c r="V19" t="n">
-        <v>60.16</v>
+        <v>47.83</v>
       </c>
       <c r="W19" t="n">
-        <v>61.63</v>
+        <v>48.62</v>
       </c>
       <c r="X19" t="n">
-        <v>63.11</v>
+        <v>49.42</v>
       </c>
       <c r="Y19" t="n">
-        <v>64.59999999999999</v>
+        <v>50.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>66.09999999999999</v>
+        <v>51.02</v>
       </c>
       <c r="AA19" t="n">
-        <v>67.61</v>
+        <v>51.86</v>
       </c>
       <c r="AB19" t="n">
-        <v>69.14</v>
+        <v>52.69</v>
       </c>
       <c r="AC19" t="n">
-        <v>70.67</v>
+        <v>53.53</v>
       </c>
       <c r="AD19" t="n">
-        <v>72.22</v>
+        <v>54.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>73.77</v>
+        <v>55.2</v>
       </c>
       <c r="AF19" t="n">
-        <v>75.34</v>
+        <v>56.05</v>
       </c>
       <c r="AG19" t="n">
-        <v>76.91</v>
+        <v>56.9</v>
       </c>
       <c r="AH19" t="n">
-        <v>78.5</v>
+        <v>57.75</v>
       </c>
       <c r="AI19" t="n">
-        <v>80.09999999999999</v>
+        <v>58.59</v>
       </c>
       <c r="AJ19" t="n">
-        <v>81.70999999999999</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ELCHTIXX03</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Output demand of dispatch-ready in Haiti</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>not needed</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>not needed</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>not needed</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>User defined</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="L20" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="P20" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="R20" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="V20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="W20" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="X20" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>6.6</v>
+        <v>59.44</v>
       </c>
     </row>
   </sheetData>
